--- a/Data_Table/증강 테이블.xlsx
+++ b/Data_Table/증강 테이블.xlsx
@@ -4559,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4655,166 +4655,181 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>판 안 장착 슬롯 기본 수 (공용 스킬 Aug_Slot 합만큼 +)</t>
+          <t>판 안 장착 슬롯 기본 수 (공용 스킬 Aug_Slot 합만큼 +, 2026-10-20 사용자: 2칸에서 시작해 조건마다 한 칸씩)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>offer_count</t>
+          <t>slot_max</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>층 클리어 때 보여 주는 증강 수 (그중 1개)</t>
+          <t>판 안 장착 슬롯 최대 (관리 창 자물쇠 미리보기도 여기까지)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pt_per_floor</t>
+          <t>offer_count</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>층 클리어 때 장착한 증강 한 개마다 강화 포인트 = 클리어 층 × 이 값</t>
+          <t>층 클리어 때 보여 주는 증강 수 (그중 1개)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>up_max</t>
+          <t>pt_per_floor</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>강화 최대 레벨</t>
+          <t>층 클리어 때 장착한 증강 한 개마다 강화 포인트 = 클리어 층 × 이 값</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>up_pct</t>
+          <t>up_max</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>강화 1레벨마다 효과 값 +이 비율 (Lv 5 = ×1.5)</t>
+          <t>강화 최대 레벨</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>up_pt_base</t>
+          <t>up_pct</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>150</v>
+        <v>0.1</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>강화 포인트 필요 = 기본 × 증가^레벨</t>
+          <t>강화 1레벨마다 효과 값 +이 비율 (Lv 5 = ×1.5)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>up_pt_grow</t>
+          <t>up_pt_base</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C12" s="1" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>강화 포인트 필요 = 기본 × 증가^레벨</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>up_cheese_base</t>
+          <t>up_pt_grow</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1623</v>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>강화 치즈 = 기본 × 스테이지 테이블 치즈 배율(최고 도달 층) × 층 배율^(min(층, 상한)-1) × 증가^레벨. 기본 = 층 치즈 수입(방 9개)의 UP_CHEESE_FLOORS 배 (Lv0→1)</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="C13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>up_cheese_grow</t>
+          <t>up_cheese_base</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C14" s="1" t="inlineStr"/>
+        <v>1623</v>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>강화 치즈 = 기본 × 스테이지 테이블 치즈 배율(최고 도달 층) × 층 배율^(min(층, 상한)-1) × 증가^레벨. 기본 = 층 치즈 수입(방 9개)의 UP_CHEESE_FLOORS 배 (Lv0→1)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>up_cheese_floor_grow</t>
+          <t>up_cheese_grow</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>1.2213</v>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>층 수입 배율 (Tools/gen_economy.fit_k, 상점 bc_floor_grow 와 같음)</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>up_cheese_floor_cap</t>
+          <t>up_cheese_floor_grow</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>30</v>
+        <v>1.2213</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>층 수입 배율을 이 층까지만</t>
+          <t>층 수입 배율 (Tools/gen_economy.fit_k, 상점 bc_floor_grow 와 같음)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>up_cheese_floor_cap</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>층 수입 배율을 이 층까지만</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>seen_reveal</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="B18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>1 = 한 번이라도 얻은 증강만 이름·설명 보임 (나머지 ???)</t>
         </is>

--- a/Data_Table/증강 테이블.xlsx
+++ b/Data_Table/증강 테이블.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Augment" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grade" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aug_Config" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No_Scale" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Augment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Grade" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Offer" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Aug_Config" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="No_Scale" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Column_Desc" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4559,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>층 클리어 때 장착한 증강 한 개마다 강화 포인트 = 클리어 층 × 이 값</t>
+          <t>(안 씀, 2026-10-21 강화 포인트 없앰) 층 클리어 때 장착한 증강 한 개마다 강화 포인트 = 클리어 층 × 이 값</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>강화 포인트 필요 = 기본 × 증가^레벨</t>
+          <t>(안 씀, 2026-10-21 강화 포인트 없앰) 강화 포인트 필요 = 기본 × 증가^레벨</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,11 @@
       <c r="B13" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="C13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(안 씀, 2026-10-21 강화 포인트 없앰) </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -4832,6 +4836,81 @@
       <c r="C18" s="1" t="inlineStr">
         <is>
           <t>1 = 한 번이라도 얻은 증강만 이름·설명 보임 (나머지 ???)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>up_copy_1</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>강화 Lv 0→1 에 드는 같은 증강 수 (2026-10-21: 강화 포인트 대신 같은 증강 소모 + 치즈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>up_copy_2</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>강화 Lv 1→2 같은 증강 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>up_copy_3</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>강화 Lv 2→3 같은 증강 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>up_copy_4</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>강화 Lv 3→4 같은 증강 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>up_copy_5</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>강화 Lv 4→5 같은 증강 수 (up_max 5)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/증강 테이블.xlsx
+++ b/Data_Table/증강 테이블.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Augment" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Grade" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Offer" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Aug_Config" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="No_Scale" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Column_Desc" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Augment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grade" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aug_Config" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No_Scale" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -774,34 +774,34 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>81102</v>
+        <v>81105</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>치즈 킁킁</t>
+          <t>강철 앞니</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>4681102</v>
+        <v>4681105</v>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>치즈 +{1%}%</t>
+          <t>벽 피해 +{1%}%</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>4781102</v>
+        <v>4781105</v>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>Cheese_Pct</t>
+          <t>Wall_Dmg_Pct</t>
         </is>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>aug_cheese</t>
+          <t>aug_wall</t>
         </is>
       </c>
       <c r="P5" s="1" t="n">
@@ -833,40 +833,40 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>Cheese Sniffer</t>
+          <t>Steel Teeth</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>81103</v>
+        <v>81106</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>야근 수당</t>
+          <t>급소 찾기</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>4681103</v>
+        <v>4681106</v>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +{1}초</t>
+          <t>치명타 확률 +{1%}%</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>4781103</v>
+        <v>4781106</v>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Crit_Chance</t>
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>8</v>
+        <v>0.04</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>aug_clock</t>
+          <t>aug_crit</t>
         </is>
       </c>
       <c r="P6" s="1" t="n">
@@ -898,40 +898,40 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>Overtime Pay</t>
+          <t>Weak Spot</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>81104</v>
+        <v>81107</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>사랑의 둥지</t>
+          <t>보스 사냥 면허</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>4681104</v>
+        <v>4681107</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>번식 확률 +{1%}%</t>
+          <t>보스 피해 +{1%}%</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>4781104</v>
+        <v>4781107</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>Breed_Chance</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>0</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>aug_heart</t>
+          <t>aug_boss</t>
         </is>
       </c>
       <c r="P7" s="1" t="n">
@@ -963,40 +963,40 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>Love Nest</t>
+          <t>Boss Hunting License</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>81105</v>
+        <v>81210</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>강철 앞니</t>
+          <t>프로틴 셰이크</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>4681105</v>
+        <v>4681210</v>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>벽 피해 +{1%}%</t>
+          <t>쥐 공격력 +{1%}%</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>4781105</v>
+        <v>4781101</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>Wall_Dmg_Pct</t>
+          <t>Atk_Pct</t>
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>aug_wall</t>
+          <t>aug_protein</t>
         </is>
       </c>
       <c r="P8" s="1" t="n">
@@ -1028,32 +1028,32 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>Steel Teeth</t>
+          <t>Protein Shake</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>81106</v>
+        <v>81207</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>급소 찾기</t>
+          <t>치명적 앞니</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>4681106</v>
+        <v>4681207</v>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>치명타 확률 +{1%}%</t>
+          <t>치명타 확률 +{1%}% · 치명타 피해 +{2%}%</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>4781106</v>
+        <v>4781207</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>0</v>
@@ -1071,11 +1071,11 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Crit_Dmg</t>
         </is>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>aug_crit</t>
+          <t>aug_fang</t>
         </is>
       </c>
       <c r="P9" s="1" t="n">
@@ -1093,40 +1093,40 @@
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>Weak Spot</t>
+          <t>Deadly Fang</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>81107</v>
+        <v>81214</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>보스 사냥 면허</t>
+          <t>철거 전문가</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>4681107</v>
+        <v>4681214</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>보스 피해 +{1%}%</t>
+          <t>벽 피해 +{1%}%</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>4781107</v>
+        <v>4781105</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>Boss_Dmg_Pct</t>
+          <t>Wall_Dmg_Pct</t>
         </is>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>aug_boss</t>
+          <t>aug_demolish</t>
         </is>
       </c>
       <c r="P10" s="1" t="n">
@@ -1158,40 +1158,40 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>Boss Hunting License</t>
+          <t>Demolition Expert</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>81108</v>
+        <v>81212</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>에너지 드링크</t>
+          <t>클릭 폭격</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>4681108</v>
+        <v>4681212</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>필살기 게이지 충전 +{1%}%</t>
+          <t>클릭 총공격 때 누를 때마다 {s1%}% 확률로 폭발 (공격력 ×{s3})</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>4781108</v>
+        <v>4700001</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>Ult_Gauge_Pct</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.12</v>
+        <v>83005</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>aug_drink</t>
+          <t>aug_click</t>
         </is>
       </c>
       <c r="P11" s="1" t="n">
@@ -1223,40 +1223,40 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Energy Drink</t>
+          <t>Click Barrage</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>81109</v>
+        <v>81206</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>단칸방 확장</t>
+          <t>미다스의 앞니</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>4681109</v>
+        <v>4681206</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>최대 마리 수 +{1}</t>
+          <t>황금 물건을 부수면 치즈 +{s1%}%</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>4781109</v>
+        <v>4700002</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>Pop_Cap</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H12" s="1" t="n">
-        <v>6</v>
+        <v>83013</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>aug_nest</t>
+          <t>aug_gold</t>
         </is>
       </c>
       <c r="P12" s="1" t="n">
@@ -1288,40 +1288,40 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>Room Expansion</t>
+          <t>Midas Bite</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>81110</v>
+        <v>81213</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>연구 노트</t>
+          <t>잭팟</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>4681110</v>
+        <v>4681213</v>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>층 클리어 연구자료 +{1%}%</t>
+          <t>층 클리어 때 {s1%}% 확률로 연구자료 ×{s2}</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>4781110</v>
+        <v>4781213</v>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>Research_Pct</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.15</v>
+        <v>83012</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>0</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>aug_note</t>
+          <t>aug_jackpot</t>
         </is>
       </c>
       <c r="P13" s="1" t="n">
@@ -1353,54 +1353,54 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>Research Notes</t>
+          <t>Jackpot</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>81111</v>
+        <v>81306</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>개박하 알레르기</t>
+          <t>보스 킬러</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>4681111</v>
+        <v>4681306</v>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>고양이 체력 -{1%}% · 겁먹는 시간 -{1b%}%</t>
+          <t>보스 피해 +{1%}% · 필살기 게이지 +{2%}%</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>4781111</v>
+        <v>4781306</v>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>Cat_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Ult_Gauge_Pct</t>
         </is>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>0</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>aug_cat</t>
+          <t>aug_skull</t>
         </is>
       </c>
       <c r="P14" s="1" t="n">
@@ -1418,40 +1418,40 @@
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>Catnip Allergy</t>
+          <t>Boss Killer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>81112</v>
+        <v>81315</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>날쌘 발</t>
+          <t>강철 턱</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>4681112</v>
+        <v>4681315</v>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>이동 속도 +{1%}%</t>
+          <t>쥐 공격력 +{1%}% · 벽 피해 +{2%}%</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>4781112</v>
+        <v>4781315</v>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>Move_Speed_Pct</t>
+          <t>Atk_Pct</t>
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>0</v>
@@ -1461,11 +1461,11 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Wall_Dmg_Pct</t>
         </is>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>aug_feet</t>
+          <t>aug_jaw</t>
         </is>
       </c>
       <c r="P15" s="1" t="n">
@@ -1483,24 +1483,24 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>Quick Feet</t>
+          <t>Iron Jaw</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>81201</v>
+        <v>81307</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>연타의 달인</t>
+          <t>다다다다</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>4681201</v>
+        <v>4681307</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>0</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>aug_combo</t>
+          <t>aug_rapid</t>
         </is>
       </c>
       <c r="P16" s="1" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>Combo Master</t>
+          <t>Rat-a-tat</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>81202</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
@@ -1619,34 +1619,34 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>81203</v>
+        <v>81313</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>쌍둥이 유전자</t>
+          <t>연쇄 붕괴</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>4681203</v>
+        <v>4681313</v>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>쌍둥이 확률 +{1%}%</t>
+          <t>벽 하나가 무너지면 남은 벽 체력 -{s1%}%</t>
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>4781203</v>
+        <v>4781313</v>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>Twin_Chance</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.1</v>
+        <v>83010</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>aug_twin</t>
+          <t>aug_domino</t>
         </is>
       </c>
       <c r="P18" s="1" t="n">
@@ -1678,40 +1678,40 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>Twin Genes</t>
+          <t>Domino Walls</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>81204</v>
+        <v>81314</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>필살 수련</t>
+          <t>승급 폭죽</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>4681204</v>
+        <v>4681314</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>필살기 피해 +{1%}%</t>
+          <t>승급할 때 새 쥐 자리에서 폭죽 폭발 (공격력 ×{s2})</t>
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>4781204</v>
+        <v>4700003</v>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>Ult_Power_Pct</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.4</v>
+        <v>83011</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>aug_ult</t>
+          <t>aug_rankboom</t>
         </is>
       </c>
       <c r="P19" s="1" t="n">
@@ -1743,54 +1743,54 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>Ult Training</t>
+          <t>Promotion Fireworks</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>81205</v>
+        <v>81316</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>돌격 나팔</t>
+          <t>쥐 탑 쌓기</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>4681205</v>
+        <v>4681316</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>총공격 시간 +{1}초 · 위력 +{1b} · 쿨타임 -{2}초</t>
+          <t>장착하면 쥐 {s2}마리씩 쌓아 합친 쥐 탑 {s1}개 (능력치 합산, 판 끝까지)</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>4781205</v>
+        <v>4781316</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>Rush_Up</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1</v>
+        <v>83014</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>Rush_CD</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L20" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>aug_bugle</t>
+          <t>aug_tower</t>
         </is>
       </c>
       <c r="P20" s="1" t="n">
@@ -1808,43 +1808,43 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>Charge Bugle</t>
+          <t>Rat Tower</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>81206</v>
+        <v>81311</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>미다스의 앞니</t>
+          <t>천둥 번개</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>4681206</v>
+        <v>4681311</v>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>황금 물건 확률 +{1%}%</t>
+          <t>{s1}초마다 먹구름에서 번개 {s2}개 (공격력 ×{s3})</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>4781206</v>
+        <v>4700004</v>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>Gold_Item</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.05</v>
+        <v>83004</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>0</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>aug_gold</t>
+          <t>aug_storm</t>
         </is>
       </c>
       <c r="P21" s="1" t="n">
@@ -1873,40 +1873,40 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>Midas Bite</t>
+          <t>Thunderstorm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>81207</v>
+        <v>81317</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>치명적 앞니</t>
+          <t>치즈 비</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>4681207</v>
+        <v>4681317</v>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>치명타 확률 +{1%}% · 치명타 피해 +{2%}%</t>
+          <t>{s1}초마다 {s2}초 동안 치즈 비 (치즈 +{s3%}%)</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>4781207</v>
+        <v>4781317</v>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>Crit_Chance</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.06</v>
+        <v>83015</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>0</v>
@@ -1916,11 +1916,11 @@
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>Crit_Dmg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L22" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>aug_fang</t>
+          <t>aug_cheeserain</t>
         </is>
       </c>
       <c r="P22" s="1" t="n">
@@ -1938,46 +1938,46 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>Deadly Fang</t>
+          <t>Cheese Rain</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>81208</v>
+        <v>81303</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>서류 도둑</t>
+          <t>탄생 축제</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>4681208</v>
+        <v>4681303</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>층 클리어 연구자료 +{1%}%</t>
+          <t>새끼가 태어나면 주변 쥐 {1}초 광란</t>
         </is>
       </c>
       <c r="F23" s="1" t="n">
-        <v>4781110</v>
+        <v>4781303</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>Research_Pct</t>
+          <t>Birth_Frenzy</t>
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.35</v>
+        <v>4</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>aug_papers</t>
+          <t>aug_party</t>
         </is>
       </c>
       <c r="P23" s="1" t="n">
@@ -2003,40 +2003,40 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>Paper Thief</t>
+          <t>Birth Party</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>81209</v>
+        <v>81318</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>부실 공사</t>
+          <t>골든 햄스터 생쥐</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>4681209</v>
+        <v>4681318</v>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>벽 체력 -{1%}%</t>
+          <t>일반 쥐 전원 골든 햄스터 · 늘 공으로 굴러다님 (이후 태어나는 쥐도)</t>
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>4781209</v>
+        <v>4781318</v>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>Wall_Hp_Down</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.08</v>
+        <v>83016</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>aug_crack</t>
+          <t>aug_u_hamster</t>
         </is>
       </c>
       <c r="P24" s="1" t="n">
@@ -2068,40 +2068,40 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>Shoddy Walls</t>
+          <t>Golden Hamster Rats</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>81210</v>
+        <v>81319</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>프로틴 셰이크</t>
+          <t>판다 잠옷 정글리안 생쥐</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>4681210</v>
+        <v>4681319</v>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>쥐 공격력 +{1%}%</t>
+          <t>일반 쥐 전원 판다 잠옷 정글리안 · 늘 공으로 굴러다님 (이후 태어나는 쥐도)</t>
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>4781101</v>
+        <v>4781319</v>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>Atk_Pct</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.3</v>
+        <v>83017</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>0</v>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>aug_protein</t>
+          <t>aug_u_panda</t>
         </is>
       </c>
       <c r="P25" s="1" t="n">
@@ -2133,40 +2133,40 @@
       </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>Protein Shake</t>
+          <t>Panda Pajama Rats</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>81212</v>
+        <v>81403</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>클릭 폭격</t>
+          <t>전설의 앞니</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>4681212</v>
+        <v>4681403</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>클릭 총공격 때 누른 곳에 작은 폭발 {s1}번 (공격력 ×{s3})</t>
+          <t>쥐 공격력 +{1%}% · 모든 피해 +{2%}%</t>
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>4781212</v>
+        <v>4781403</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Atk_Pct</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>83005</v>
+        <v>1</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>0</v>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Dmg_Pct</t>
         </is>
       </c>
       <c r="L26" s="1" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>0</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>aug_click</t>
+          <t>aug_crown</t>
         </is>
       </c>
       <c r="P26" s="1" t="n">
@@ -2198,32 +2198,32 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>Click Barrage</t>
+          <t>Legendary Incisors</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>81213</v>
+        <v>81409</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>회전 치즈 칼날</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>4681213</v>
+        <v>4681409</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>층 클리어 때 {s1%}% 확률로 연구자료 ×{s2}</t>
+          <t>칠 때 {s1%}% 확률로 그 쥐 둘레를 치즈 칼날 {s2}개가 {s5}초 돌며 공격 (공격력 ×{s4})</t>
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>4781213</v>
+        <v>4700005</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>83012</v>
+        <v>83003</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>aug_jackpot</t>
+          <t>aug_blades</t>
         </is>
       </c>
       <c r="P27" s="1" t="n">
@@ -2263,40 +2263,40 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>Jackpot</t>
+          <t>Spinning Cheese Blades</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>81211</v>
+        <v>81408</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>연장 근무</t>
+          <t>거대 쥐 출현</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>4681211</v>
+        <v>4681408</v>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +{1}초</t>
+          <t>{s1}초마다 쥐 {s2}마리가 {s5}초 동안 거대화 (공격력 ×{s4})</t>
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>4781103</v>
+        <v>4781408</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>18</v>
+        <v>83001</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>aug_clock2</t>
+          <t>aug_giant</t>
         </is>
       </c>
       <c r="P28" s="1" t="n">
@@ -2328,43 +2328,43 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Rise of the Giants</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>81301</v>
+        <v>81413</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>치즈 운석우</t>
+          <t>분신 소환</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>4681301</v>
+        <v>4681413</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>{1}초마다 치즈 운석 (위력 +{1b%}%)</t>
+          <t>{s1}초마다 가장 강한 쥐의 거대 분신 {s2}마리가 {s3}초 동안 싸움</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>4781301</v>
+        <v>4781413</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>Cheese_Meteor</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>10</v>
+        <v>83018</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1" t="n">
         <v>0</v>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>aug_meteor</t>
+          <t>aug_clones</t>
         </is>
       </c>
       <c r="P29" s="1" t="n">
@@ -2393,43 +2393,43 @@
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>Cheese Meteor Shower</t>
+          <t>Clone Summon</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>81302</v>
+        <v>81414</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>연쇄 폭발</t>
+          <t>운석 소환</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>4681302</v>
+        <v>4681414</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>물건이 터질 때 연쇄 폭발 범위 +{1} · 피해 +{1b%}%</t>
+          <t>{s1}초마다 큰 치즈 운석 낙하 (공격력 ×{s3})</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>4781302</v>
+        <v>4781414</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>Chain_Blast</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>60</v>
+        <v>83019</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>aug_blast</t>
+          <t>aug_meteor</t>
         </is>
       </c>
       <c r="P30" s="1" t="n">
@@ -2458,46 +2458,46 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>Chain Reaction</t>
+          <t>Meteor Strike</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>81303</v>
+        <v>81412</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>탄생 축제</t>
+          <t>쥐 토네이도</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>4681303</v>
+        <v>4681412</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>새끼가 태어나면 주변 쥐 {1}초 광란</t>
+          <t>{s1}초마다 토네이도가 {s2}초 동안 방을 휩씀 (초당 공격력 ×{s4})</t>
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>4781303</v>
+        <v>4781412</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>Birth_Frenzy</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>4</v>
+        <v>83009</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>aug_party</t>
+          <t>aug_tornado</t>
         </is>
       </c>
       <c r="P31" s="1" t="n">
@@ -2523,40 +2523,40 @@
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>Birth Party</t>
+          <t>Rat Tornado</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>81304</v>
+        <v>81415</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>시간 도둑</t>
+          <t>장난감 기차</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>4681304</v>
+        <v>4681415</v>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +{1}초 · 쥐 공격력 +{2%}%</t>
+          <t>{s1}초마다 기차가 맵을 가로지름 (공격력 ×{s3})</t>
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>4781304</v>
+        <v>4781415</v>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>25</v>
+        <v>83020</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>0</v>
@@ -2566,11 +2566,11 @@
       </c>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>Atk_Pct</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L32" s="1" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>aug_hourglass</t>
+          <t>aug_train</t>
         </is>
       </c>
       <c r="P32" s="1" t="n">
@@ -2588,40 +2588,40 @@
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>Time Thief</t>
+          <t>Toy Train</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>81305</v>
+        <v>81416</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>쥐 아파트</t>
+          <t>스케이터 생쥐</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>4681305</v>
+        <v>4681416</v>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>최대 마리 수 +{1} · 번식 확률 +{2%}%</t>
+          <t>레어 쥐 전원 양복 대머리 생쥐 · 매우 빠르게 달리며 박치기 (이후 태어나는 쥐도)</t>
         </is>
       </c>
       <c r="F33" s="1" t="n">
-        <v>4781305</v>
+        <v>4781416</v>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>Pop_Cap</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>15</v>
+        <v>83021</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>0</v>
@@ -2631,11 +2631,11 @@
       </c>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>Breed_Chance</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L33" s="1" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>aug_apart</t>
+          <t>aug_u_skater</t>
         </is>
       </c>
       <c r="P33" s="1" t="n">
@@ -2653,40 +2653,40 @@
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>Rat Apartment</t>
+          <t>Skater Rats</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>81306</v>
+        <v>81417</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>보스 킬러</t>
+          <t>맘스땃쥐 생쥐</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>4681306</v>
+        <v>4681417</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>보스 피해 +{1%}% · 필살기 게이지 +{2%}%</t>
+          <t>에픽 쥐 전원 맘스땃쥐 · 패티 최대 {s5}장 · 박치기 피해 +{s4%}% (이후 태어나는 쥐도)</t>
         </is>
       </c>
       <c r="F34" s="1" t="n">
-        <v>4781306</v>
+        <v>4781417</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>Boss_Dmg_Pct</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.6</v>
+        <v>83022</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>0</v>
@@ -2696,11 +2696,11 @@
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>Ult_Gauge_Pct</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L34" s="1" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>aug_skull</t>
+          <t>aug_u_burger</t>
         </is>
       </c>
       <c r="P34" s="1" t="n">
@@ -2718,43 +2718,43 @@
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
-          <t>Boss Killer</t>
+          <t>Burger Rats</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>81307</v>
+        <v>81418</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>다다다다</t>
+          <t>5G 생쥐</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>4681307</v>
+        <v>4681418</v>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>부딪힐 때 {1%}% 확률로 {1b}번 더 공격</t>
+          <t>에픽 쥐 전원 5G · 동료 수와 상관없이 모든 쥐에게 데이터 전송 (이후 태어나는 쥐도)</t>
         </is>
       </c>
       <c r="F35" s="1" t="n">
-        <v>4781201</v>
+        <v>4781418</v>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>Multi_Hit</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.25</v>
+        <v>83023</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>aug_rapid</t>
+          <t>aug_u_fiveg</t>
         </is>
       </c>
       <c r="P35" s="1" t="n">
@@ -2783,1242 +2783,7 @@
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>Rat-a-tat</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>81308</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>두 배 승급</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>4681308</v>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>승급할 때 {1%}% 확률로 2마리</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>4781308</v>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>Promote_Double</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t>aug_double</t>
-        </is>
-      </c>
-      <c r="P36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="1" t="inlineStr">
-        <is>
-          <t>Double Promotion</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>81309</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>번개 앞니</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>4681309</v>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>물 때 {1%}% 확률로 주변 물건 {1b}개 감전</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>4781202</v>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>Bite_Zap</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I37" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t>aug_thunder</t>
-        </is>
-      </c>
-      <c r="P37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="1" t="inlineStr">
-        <is>
-          <t>Thunder Fang</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>81310</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>눈덩이 굴리기</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>4681310</v>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>이번 층에서 물건을 부술 때마다 공격력 +{s1%}% (최대 {s2%}%)</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="n">
-        <v>4781310</v>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H38" s="1" t="n">
-        <v>83002</v>
-      </c>
-      <c r="I38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="1" t="inlineStr">
-        <is>
-          <t>aug_snowball</t>
-        </is>
-      </c>
-      <c r="P38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="1" t="inlineStr">
-        <is>
-          <t>Snowball</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>81311</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>천둥 번개</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>4681311</v>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>{s1}초마다 대상 {s2}곳에 번개 (공격력 ×{s3})</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="n">
-        <v>4781311</v>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H39" s="1" t="n">
-        <v>83004</v>
-      </c>
-      <c r="I39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="1" t="inlineStr">
-        <is>
-          <t>aug_storm</t>
-        </is>
-      </c>
-      <c r="P39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q39" s="1" t="inlineStr">
-        <is>
-          <t>Thunderstorm</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>81312</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>세포 분열</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>4681312</v>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>물건을 부수면 {s1%}% 확률로 임시 쥐 ({s2}초)</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="n">
-        <v>4781312</v>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H40" s="1" t="n">
-        <v>83006</v>
-      </c>
-      <c r="I40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t>aug_mitosis</t>
-        </is>
-      </c>
-      <c r="P40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t>Mitosis</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>81313</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>연쇄 붕괴</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>4681313</v>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>벽 하나가 무너지면 남은 벽 체력 -{s1%}%</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="n">
-        <v>4781313</v>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="n">
-        <v>83010</v>
-      </c>
-      <c r="I41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="1" t="inlineStr">
-        <is>
-          <t>aug_domino</t>
-        </is>
-      </c>
-      <c r="P41" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="1" t="inlineStr">
-        <is>
-          <t>Domino Walls</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>81314</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>승급 폭죽</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>4681314</v>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>승급할 때 새 쥐 자리에서 폭발 (공격력 ×{s2})</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="n">
-        <v>4781314</v>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="n">
-        <v>83011</v>
-      </c>
-      <c r="I42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="1" t="inlineStr">
-        <is>
-          <t>aug_rankboom</t>
-        </is>
-      </c>
-      <c r="P42" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="1" t="inlineStr">
-        <is>
-          <t>Promotion Fireworks</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>81401</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>자동 필살 장치</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>4681401</v>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>필살기 자동 사용 · 필살기 게이지 +{2%}%</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>4781401</v>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>Ult_Auto</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>Ult_Gauge_Pct</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="1" t="inlineStr">
-        <is>
-          <t>aug_robot</t>
-        </is>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q43" s="1" t="inlineStr">
-        <is>
-          <t>Auto-Ult Device</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>81402</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>쥐 떼 군단</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>4681402</v>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>최대 마리 수 +{1} · 쌍둥이 확률 +{2%}%</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="n">
-        <v>4781402</v>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>Pop_Cap</t>
-        </is>
-      </c>
-      <c r="H44" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="I44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>Twin_Chance</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="1" t="inlineStr">
-        <is>
-          <t>aug_legion</t>
-        </is>
-      </c>
-      <c r="P44" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q44" s="1" t="inlineStr">
-        <is>
-          <t>Rat Legion</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>81403</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>전설의 앞니</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>4681403</v>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>쥐 공격력 +{1%}% · 모든 피해 +{2%}%</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="n">
-        <v>4781403</v>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>Atk_Pct</t>
-        </is>
-      </c>
-      <c r="H45" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>Dmg_Pct</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="1" t="inlineStr">
-        <is>
-          <t>aug_crown</t>
-        </is>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" s="1" t="inlineStr">
-        <is>
-          <t>Legendary Incisors</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>81404</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>연구소 털이</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>4681404</v>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>층 클리어 연구자료 +{1%}% · 치즈 +{2%}%</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="n">
-        <v>4781404</v>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>Research_Pct</t>
-        </is>
-      </c>
-      <c r="H46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>Cheese_Pct</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t>aug_vault</t>
-        </is>
-      </c>
-      <c r="P46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t>Lab Heist</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>81405</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>시간 정지</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>4681405</v>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>층 제한시간 +{1}초 · 벽 체력 -{2%}%</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="n">
-        <v>4781405</v>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>Time_Add</t>
-        </is>
-      </c>
-      <c r="H47" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="I47" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>Wall_Hp_Down</t>
-        </is>
-      </c>
-      <c r="L47" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M47" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="1" t="inlineStr">
-        <is>
-          <t>aug_stop</t>
-        </is>
-      </c>
-      <c r="P47" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" s="1" t="inlineStr">
-        <is>
-          <t>Time Stop</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>81406</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>치즈 종말</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>4681406</v>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>{1}초마다 치즈 운석 (위력 +{1b%}%) · 연쇄 폭발 범위 +{2}</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="n">
-        <v>4781406</v>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>Cheese_Meteor</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I48" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>Chain_Blast</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="M48" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="1" t="inlineStr">
-        <is>
-          <t>aug_doom</t>
-        </is>
-      </c>
-      <c r="P48" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="1" t="inlineStr">
-        <is>
-          <t>Cheesepocalypse</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>81407</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>필살기 폭주</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>4681407</v>
-      </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>필살기 피해 +{1%}% · 필살기 게이지 +{2%}%</t>
-        </is>
-      </c>
-      <c r="F49" s="1" t="n">
-        <v>4781407</v>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>Ult_Power_Pct</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>Ult_Gauge_Pct</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>aug_overdrive</t>
-        </is>
-      </c>
-      <c r="P49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q49" s="1" t="inlineStr">
-        <is>
-          <t>Ult Overdrive</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>81408</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>거대 쥐 출현</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>4681408</v>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>{s1}초마다 쥐 {s2}마리가 {s5}초 동안 거대화 (공격력 ×{s4})</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="n">
-        <v>4781408</v>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>83001</v>
-      </c>
-      <c r="I50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="1" t="inlineStr">
-        <is>
-          <t>aug_giant</t>
-        </is>
-      </c>
-      <c r="P50" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="1" t="inlineStr">
-        <is>
-          <t>Rise of the Giants</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>81409</v>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>회전 치즈 칼날</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>4681409</v>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>쥐 무리 둘레를 치즈 칼날 {s1}개가 돌며 공격 (공격력 ×{s3})</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="n">
-        <v>4781409</v>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H51" s="1" t="n">
-        <v>83003</v>
-      </c>
-      <c r="I51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="1" t="inlineStr">
-        <is>
-          <t>aug_blades</t>
-        </is>
-      </c>
-      <c r="P51" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q51" s="1" t="inlineStr">
-        <is>
-          <t>Spinning Cheese Blades</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>81410</v>
-      </c>
-      <c r="B52" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>시간 역행</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>4681410</v>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>제한시간이 0 이 되면 {s1}초를 되돌림 (판당 {s2}번)</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="n">
-        <v>4781410</v>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>83007</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="1" t="inlineStr">
-        <is>
-          <t>aug_rewind</t>
-        </is>
-      </c>
-      <c r="P52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="1" t="inlineStr">
-        <is>
-          <t>Time Rewind</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>81411</v>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>필살기 메아리</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>4681411</v>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>필살기가 끝나면 {s1%}% 확률로 다른 쥐의 필살기가 한 번 더</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="n">
-        <v>4781411</v>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>83008</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="1" t="inlineStr">
-        <is>
-          <t>aug_echo</t>
-        </is>
-      </c>
-      <c r="P53" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q53" s="1" t="inlineStr">
-        <is>
-          <t>Ultimate Echo</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>81412</v>
-      </c>
-      <c r="B54" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>쥐 토네이도</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>4681412</v>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>{s1}초마다 토네이도가 {s2}초 동안 방을 휩씀 (초당 공격력 ×{s4})</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="n">
-        <v>4781412</v>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>83009</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="1" t="inlineStr">
-        <is>
-          <t>aug_tornado</t>
-        </is>
-      </c>
-      <c r="P54" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="1" t="inlineStr">
-        <is>
-          <t>Rat Tornado</t>
+          <t>5G Rats</t>
         </is>
       </c>
     </row>
@@ -4434,16 +3199,16 @@
         <v>31</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -4451,16 +3216,16 @@
         <v>41</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4468,16 +3233,16 @@
         <v>51</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -4485,16 +3250,16 @@
         <v>61</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>37</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -4502,16 +3267,16 @@
         <v>71</v>
       </c>
       <c r="B8" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>39</v>
-      </c>
       <c r="D8" s="1" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -4519,16 +3284,16 @@
         <v>81</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -4536,16 +3301,16 @@
         <v>91</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4559,7 +3324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4704,7 +3469,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>(안 씀, 2026-10-21 강화 포인트 없앰) 층 클리어 때 장착한 증강 한 개마다 강화 포인트 = 클리어 층 × 이 값</t>
+          <t>층 클리어 때 장착한 증강 한 개마다 강화 포인트 = 클리어 층 × 이 값</t>
         </is>
       </c>
     </row>
@@ -4749,7 +3514,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>(안 씀, 2026-10-21 강화 포인트 없앰) 강화 포인트 필요 = 기본 × 증가^레벨</t>
+          <t>강화 포인트 필요 = 기본 × 증가^레벨</t>
         </is>
       </c>
     </row>
@@ -4762,11 +3527,7 @@
       <c r="B13" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(안 씀, 2026-10-21 강화 포인트 없앰) </t>
-        </is>
-      </c>
+      <c r="C13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -4842,75 +3603,465 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>up_copy_1</t>
+          <t>replace_81102</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>1</v>
+        <v>81101</v>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>강화 Lv 0→1 에 드는 같은 증강 수 (2026-10-21: 강화 포인트 대신 같은 증강 소모 + 치즈)</t>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>up_copy_2</t>
+          <t>replace_81103</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>1</v>
+        <v>81105</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>강화 Lv 1→2 같은 증강 수</t>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>up_copy_3</t>
+          <t>replace_81104</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>1</v>
+        <v>81106</v>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>강화 Lv 2→3 같은 증강 수</t>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>up_copy_4</t>
+          <t>replace_81108</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>2</v>
+        <v>81107</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>강화 Lv 3→4 같은 증강 수</t>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>up_copy_5</t>
+          <t>replace_81109</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>2</v>
+        <v>81101</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>강화 Lv 4→5 같은 증강 수 (up_max 5)</t>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>replace_81110</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>81105</v>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>replace_81111</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>81106</v>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>replace_81112</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>81107</v>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>replace_81201</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>81210</v>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>replace_81203</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>81207</v>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>replace_81204</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>81214</v>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>replace_81205</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>81212</v>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>replace_81208</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>81206</v>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>replace_81209</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>81213</v>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>replace_81211</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>81210</v>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>replace_81301</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>81306</v>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>replace_81302</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>81315</v>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>replace_81304</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>81307</v>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>replace_81305</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>81202</v>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>replace_81308</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>81313</v>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>replace_81309</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>81314</v>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>replace_81310</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>81311</v>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>replace_81312</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>81303</v>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>replace_81401</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>81403</v>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>replace_81402</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>81409</v>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>replace_81404</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>81408</v>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>replace_81405</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>81413</v>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>replace_81406</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>81414</v>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>replace_81407</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>81412</v>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>replace_81410</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>81415</v>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>replace_81411</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>81403</v>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5032,58 +4183,13 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Cheese_Meteor</t>
+          <t>Multi_Hit</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>강화해도 안 커지는 칸 (개수·간격·켜기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Gold_Item</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>강화해도 안 커지는 칸 (개수·간격·켜기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Multi_Hit</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>강화해도 안 커지는 칸 (개수·간격·켜기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ult_Auto</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>강화해도 안 커지는 칸 (개수·간격·켜기)</t>
         </is>

--- a/Data_Table/증강 테이블.xlsx
+++ b/Data_Table/증강 테이블.xlsx
@@ -3324,7 +3324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3603,41 +3603,41 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>replace_81102</t>
+          <t>unify_scale</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>81101</v>
+        <v>1.4</v>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+          <t>등급 통일 증강으로 바뀐 쥐 크기 배율 (장착 중만, 2026-10-23 사용자: 잘 보이게 크게)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>replace_81103</t>
+          <t>unify_scale_10085</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>81105</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+          <t>맘스땃쥐는 원래 잘 보여서 그대로 (unify_scale_&lt;character_id&gt; = 그 쥐만 따로)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>replace_81104</t>
+          <t>replace_81102</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>81106</v>
+        <v>81101</v>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
@@ -3648,11 +3648,11 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>replace_81108</t>
+          <t>replace_81103</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>81107</v>
+        <v>81105</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
@@ -3663,11 +3663,11 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>replace_81109</t>
+          <t>replace_81104</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>81101</v>
+        <v>81106</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
@@ -3678,11 +3678,11 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>replace_81110</t>
+          <t>replace_81108</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>81105</v>
+        <v>81107</v>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
@@ -3693,11 +3693,11 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>replace_81111</t>
+          <t>replace_81109</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>81106</v>
+        <v>81101</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
@@ -3708,11 +3708,11 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>replace_81112</t>
+          <t>replace_81110</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>81107</v>
+        <v>81105</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -3723,11 +3723,11 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>replace_81201</t>
+          <t>replace_81111</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>81210</v>
+        <v>81106</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -3738,11 +3738,11 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>replace_81203</t>
+          <t>replace_81112</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>81207</v>
+        <v>81107</v>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
@@ -3753,11 +3753,11 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>replace_81204</t>
+          <t>replace_81201</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>81214</v>
+        <v>81210</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -3768,11 +3768,11 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>replace_81205</t>
+          <t>replace_81203</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>81212</v>
+        <v>81207</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -3783,11 +3783,11 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>replace_81208</t>
+          <t>replace_81204</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>81206</v>
+        <v>81214</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
@@ -3798,11 +3798,11 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>replace_81209</t>
+          <t>replace_81205</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>81213</v>
+        <v>81212</v>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
@@ -3813,11 +3813,11 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>replace_81211</t>
+          <t>replace_81208</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>81210</v>
+        <v>81206</v>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
@@ -3828,11 +3828,11 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>replace_81301</t>
+          <t>replace_81209</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>81306</v>
+        <v>81213</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -3843,11 +3843,11 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>replace_81302</t>
+          <t>replace_81211</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>81315</v>
+        <v>81210</v>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
@@ -3858,11 +3858,11 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>replace_81304</t>
+          <t>replace_81301</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>81307</v>
+        <v>81306</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -3873,11 +3873,11 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>replace_81305</t>
+          <t>replace_81302</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>81202</v>
+        <v>81315</v>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
@@ -3888,11 +3888,11 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>replace_81308</t>
+          <t>replace_81304</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>81313</v>
+        <v>81307</v>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
@@ -3903,11 +3903,11 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>replace_81309</t>
+          <t>replace_81305</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>81314</v>
+        <v>81202</v>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
@@ -3918,11 +3918,11 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>replace_81310</t>
+          <t>replace_81308</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>81311</v>
+        <v>81313</v>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
@@ -3933,11 +3933,11 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>replace_81312</t>
+          <t>replace_81309</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>81303</v>
+        <v>81314</v>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
@@ -3948,11 +3948,11 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>replace_81401</t>
+          <t>replace_81310</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>81403</v>
+        <v>81311</v>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
@@ -3963,11 +3963,11 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>replace_81402</t>
+          <t>replace_81312</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>81409</v>
+        <v>81303</v>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
@@ -3978,11 +3978,11 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>replace_81404</t>
+          <t>replace_81401</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>81408</v>
+        <v>81403</v>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
@@ -3993,11 +3993,11 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>replace_81405</t>
+          <t>replace_81402</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>81413</v>
+        <v>81409</v>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
@@ -4008,11 +4008,11 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>replace_81406</t>
+          <t>replace_81404</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>81414</v>
+        <v>81408</v>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
@@ -4023,11 +4023,11 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>replace_81407</t>
+          <t>replace_81405</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>81412</v>
+        <v>81413</v>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
@@ -4038,11 +4038,11 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>replace_81410</t>
+          <t>replace_81406</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>81415</v>
+        <v>81414</v>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
@@ -4053,13 +4053,43 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
+          <t>replace_81407</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>81412</v>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>replace_81410</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>81415</v>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
           <t>replace_81411</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B51" s="1" t="n">
         <v>81403</v>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>없어진 증강 (기획서 Ver.04) → 같은 등급 이 증강으로 (세이브 자동 교체)</t>
         </is>
